--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="14">
   <si>
     <r>
       <t>描述</t>
@@ -174,6 +174,14 @@
   </si>
   <si>
     <t>归属</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去除编译告警</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林友滨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -601,6 +609,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -612,7 +688,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -947,15 +1023,21 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1"/>
-      <c r="B2" s="8"/>
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>12</v>
+      </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="3"/>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
   <si>
     <r>
       <t>描述</t>
@@ -182,6 +182,14 @@
   </si>
   <si>
     <t>林友滨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单机不支持存储过程。在创建存储过程时，不应该报-6，报个准确一点的错误类型会更友好。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -609,74 +617,6 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -688,7 +628,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1042,16 +982,22 @@
       <c r="K2" s="2"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1"/>
-      <c r="B3" s="8"/>
+    <row r="3" spans="1:12" ht="40.5">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>14</v>
+      </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="3"/>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
   <si>
     <r>
       <t>描述</t>
@@ -192,6 +192,14 @@
     <t>谭钊波</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>C/C++/Java/Python等驱动测试用例，集成在本地的runtest.sh中，每一次执行runtest.sh脚本，可以把所有相关的测试用例跑完成，如果能够并发进行跑应该会更好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡晓均</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -502,7 +510,63 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1002,16 +1066,20 @@
       <c r="K3" s="2"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" ht="54">
       <c r="A4" s="16"/>
-      <c r="B4" s="17"/>
+      <c r="B4" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
+      <c r="I4" s="18" t="s">
+        <v>17</v>
+      </c>
       <c r="J4" s="18"/>
       <c r="K4" s="19"/>
       <c r="L4" s="20"/>
@@ -2034,17 +2102,31 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L187">
-    <cfRule type="expression" dxfId="15" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="29" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="30" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="31" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="32" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+      <formula>$J4="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
+      <formula>$J4="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+      <formula>$J4="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
+      <formula>OR($J4="CLOSED",$J4="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -2587,44 +2669,44 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L18">
-    <cfRule type="expression" dxfId="11" priority="137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="137" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="138" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="138" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="139" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="139" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="140" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="140" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="7" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="129" stopIfTrue="1">
       <formula>$J5="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="130" stopIfTrue="1">
       <formula>$J5="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="131" stopIfTrue="1">
       <formula>$J5="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="132" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="132" stopIfTrue="1">
       <formula>OR($J5="CLOSED",$J5="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D17">
-    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="5" stopIfTrue="1">
       <formula>$J17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="6" stopIfTrue="1">
       <formula>$J17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="7" stopIfTrue="1">
       <formula>$J17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
       <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <r>
       <t>描述</t>
@@ -200,6 +200,32 @@
     <t>胡晓均</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">引擎内部交互的消息应答有两种机制，有的应答消息为 MsgInternalReplyHeader（如：register的应答，获取group信息的应答等），但有的应答消息又为MsgOpReply（如获取catalog info的应答，获取任务信息的答应等）；现在把data&lt;-&gt;catalog、coord&lt;-&gt;catalog交互的所有应答都统一为MsgOpReply，并且能兼容之前的应答消息
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可维护性</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQUOIADBMAINSTREAM-897 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -510,35 +536,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill>
@@ -1067,7 +1065,9 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="54">
-      <c r="A4" s="16"/>
+      <c r="A4" s="16">
+        <v>3</v>
+      </c>
       <c r="B4" s="8" t="s">
         <v>16</v>
       </c>
@@ -1084,19 +1084,43 @@
       <c r="K4" s="19"/>
       <c r="L4" s="20"/>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="3"/>
+    <row r="5" spans="1:12" ht="121.5">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="14">
+        <v>42151</v>
+      </c>
+      <c r="L5" s="15">
+        <v>42151</v>
+      </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1"/>
@@ -2102,30 +2126,30 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L187">
-    <cfRule type="expression" dxfId="23" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="29" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="30" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="31" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="32" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="1" stopIfTrue="1">
       <formula>$J4="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="2" stopIfTrue="1">
       <formula>$J4="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="3" stopIfTrue="1">
       <formula>$J4="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="4" stopIfTrue="1">
       <formula>OR($J4="CLOSED",$J4="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2140,8 +2164,11 @@
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2669,44 +2696,44 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L18">
-    <cfRule type="expression" dxfId="19" priority="137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="137" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="138" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="138" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="139" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="139" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="140" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="140" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="15" priority="129" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="129" stopIfTrue="1">
       <formula>$J5="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="130" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="130" stopIfTrue="1">
       <formula>$J5="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="131" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="131" stopIfTrue="1">
       <formula>$J5="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="132" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="132" stopIfTrue="1">
       <formula>OR($J5="CLOSED",$J5="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D17">
-    <cfRule type="expression" dxfId="11" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
       <formula>$J17="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="6" stopIfTrue="1">
       <formula>$J17="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
       <formula>$J17="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
       <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
@@ -11,15 +11,15 @@
     <sheet name="已完成任务" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2015年'!$A$1:$L$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">已完成任务!$A$1:$L$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2015年'!$A$1:$N$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">已完成任务!$A$1:$L$2</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <r>
       <t>描述</t>
@@ -115,20 +115,6 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>责任人</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
       <t>开始时间</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -177,23 +163,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>去除编译告警</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>林友滨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>单机不支持存储过程。在创建存储过程时，不应该报-6，报个准确一点的错误类型会更友好。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>谭钊波</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C/C++/Java/Python等驱动测试用例，集成在本地的runtest.sh中，每一次执行runtest.sh脚本，可以把所有相关的测试用例跑完成，如果能够并发进行跑应该会更好</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -224,6 +198,37 @@
   </si>
   <si>
     <t xml:space="preserve">SEQUOIADBMAINSTREAM-897 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">C/C++/Java/Python等驱动测试用例，集成在本地的runtest.sh中，每一次执行runtest.sh脚本，可以把所有相关的测试用例跑完成，如果能够并发进行跑应该会更好
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">单机不支持存储过程。在创建存储过程时，不应该报-6，报个准确一点的错误类型会更友好
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">去除编译告警
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实施人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -305,7 +310,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -448,6 +453,90 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -458,7 +547,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -522,21 +611,104 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="28">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -970,34 +1142,36 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="39.75" customWidth="1"/>
     <col min="3" max="3" width="24.75" customWidth="1"/>
-    <col min="4" max="5" width="9.375" customWidth="1"/>
-    <col min="6" max="6" width="9.75" customWidth="1"/>
-    <col min="7" max="7" width="9.875" customWidth="1"/>
-    <col min="8" max="8" width="14.125" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="15.875" customWidth="1"/>
-    <col min="12" max="12" width="17.375" customWidth="1"/>
+    <col min="4" max="4" width="8.75" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="9.375" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="9" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="10.375" customWidth="1"/>
+    <col min="12" max="12" width="9.375" customWidth="1"/>
+    <col min="13" max="13" width="12.5" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="29.45" customHeight="1">
+    <row r="1" spans="1:14" ht="29.45" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>11</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
@@ -1011,25 +1185,31 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="5" t="s">
+      <c r="N1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:14" ht="27">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -1038,18 +1218,20 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="40.5">
+        <v>11</v>
+      </c>
+      <c r="J2" s="23"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" spans="1:14" ht="40.5">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -1058,18 +1240,20 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" ht="54">
+        <v>12</v>
+      </c>
+      <c r="J3" s="23"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" ht="67.5">
       <c r="A4" s="16">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
@@ -1078,51 +1262,59 @@
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="18"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="20"/>
-    </row>
-    <row r="5" spans="1:12" ht="121.5">
+        <v>13</v>
+      </c>
+      <c r="J4" s="24"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="20"/>
+    </row>
+    <row r="5" spans="1:14" ht="121.5">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>24</v>
+        <v>14</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="D5" s="8">
         <v>1.1299999999999999</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="14">
+        <v>24</v>
+      </c>
+      <c r="J5" s="32">
+        <v>42149</v>
+      </c>
+      <c r="K5" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="14">
         <v>42151</v>
       </c>
-      <c r="L5" s="15">
+      <c r="N5" s="15">
         <v>42151</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:14">
       <c r="A6" s="1"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1132,11 +1324,13 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="J6" s="23"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1146,11 +1340,13 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="J7" s="23"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="1"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1160,11 +1356,13 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="J8" s="23"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="1"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -1174,11 +1372,13 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="J9" s="23"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -1188,11 +1388,13 @@
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="20"/>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="J10" s="24"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="20"/>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="16"/>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -1202,11 +1404,13 @@
       <c r="G11" s="18"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="20"/>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="J11" s="24"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="20"/>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="1"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -1216,11 +1420,13 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="J12" s="23"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="1"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -1230,11 +1436,13 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="J13" s="23"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="1"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -1244,11 +1452,13 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="J14" s="23"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="1"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -1258,11 +1468,13 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="J15" s="23"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="1"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -1272,11 +1484,13 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="J16" s="23"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="1"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -1286,11 +1500,13 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="J17" s="23"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="1"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -1300,11 +1516,13 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="J18" s="23"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="1"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -1314,11 +1532,13 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="J19" s="23"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="1"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -1328,11 +1548,13 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="J20" s="23"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="1"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -1342,11 +1564,13 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="J21" s="23"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="1"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -1356,11 +1580,13 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="J22" s="23"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="1"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -1370,11 +1596,13 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="J23" s="23"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="1"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -1384,11 +1612,13 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="J24" s="23"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="1"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -1398,11 +1628,13 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="J25" s="23"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="1"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -1412,11 +1644,13 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="J26" s="23"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="1"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -1426,11 +1660,13 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="J27" s="23"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="1"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -1440,11 +1676,13 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="J28" s="23"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="9"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -1454,11 +1692,13 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="10"/>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="J29" s="25"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="10"/>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="9"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -1468,11 +1708,13 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="10"/>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="J30" s="25"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="10"/>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="9"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -1482,11 +1724,13 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="10"/>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="J31" s="25"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="10"/>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="9"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -1496,11 +1740,13 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="10"/>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="J32" s="25"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="10"/>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="9"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -1510,11 +1756,13 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="10"/>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="J33" s="25"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="10"/>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="9"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -1524,11 +1772,13 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="10"/>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="J34" s="25"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="10"/>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="9"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -1538,11 +1788,13 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="10"/>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="J35" s="25"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="10"/>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="9"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -1552,25 +1804,29 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="10"/>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="J36" s="25"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="10"/>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="1"/>
       <c r="B37" s="8"/>
-      <c r="C37" s="23"/>
+      <c r="C37" s="21"/>
       <c r="D37" s="8"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="3"/>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="J37" s="23"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="3"/>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="9"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -1580,11 +1836,13 @@
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="10"/>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="J38" s="25"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="10"/>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="9"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -1594,11 +1852,13 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="10"/>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="J39" s="25"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="10"/>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="9"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -1608,11 +1868,13 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="10"/>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="J40" s="25"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="10"/>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="9"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -1622,11 +1884,13 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="10"/>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="J41" s="25"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="10"/>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="9"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -1636,11 +1900,13 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="10"/>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="J42" s="25"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="10"/>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="9"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -1650,11 +1916,13 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="10"/>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="J43" s="25"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="10"/>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="1"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -1664,11 +1932,13 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="J44" s="23"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="9"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -1678,11 +1948,13 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="10"/>
-    </row>
-    <row r="46" spans="1:12">
+      <c r="J45" s="25"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="10"/>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="9"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -1692,11 +1964,13 @@
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="10"/>
-    </row>
-    <row r="47" spans="1:12">
+      <c r="J46" s="25"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="10"/>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="9"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -1706,11 +1980,13 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="10"/>
-    </row>
-    <row r="48" spans="1:12">
+      <c r="J47" s="25"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="10"/>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="9"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -1720,11 +1996,13 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="10"/>
-    </row>
-    <row r="49" spans="1:12">
+      <c r="J48" s="25"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="10"/>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="9"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -1734,11 +2012,13 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="10"/>
-    </row>
-    <row r="50" spans="1:12">
+      <c r="J49" s="25"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="10"/>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="9"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -1748,11 +2028,13 @@
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
-      <c r="L50" s="10"/>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="J50" s="25"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="10"/>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="9"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -1762,11 +2044,13 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="10"/>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="J51" s="25"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="10"/>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="9"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -1776,11 +2060,13 @@
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
-      <c r="J52" s="8"/>
-      <c r="K52" s="8"/>
-      <c r="L52" s="10"/>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="J52" s="25"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="10"/>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="9"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -1790,11 +2076,13 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="10"/>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="J53" s="25"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="10"/>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="9"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -1804,11 +2092,13 @@
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-      <c r="L54" s="10"/>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="J54" s="25"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="10"/>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" s="9"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -1818,11 +2108,13 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="10"/>
-    </row>
-    <row r="56" spans="1:12">
+      <c r="J55" s="25"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="10"/>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" s="9"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -1832,11 +2124,13 @@
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
-      <c r="J56" s="8"/>
-      <c r="K56" s="8"/>
-      <c r="L56" s="10"/>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="J56" s="25"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="10"/>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" s="9"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -1846,11 +2140,13 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="10"/>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="J57" s="25"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="10"/>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" s="9"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -1860,11 +2156,13 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="10"/>
-    </row>
-    <row r="59" spans="1:12">
+      <c r="J58" s="25"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="8"/>
+      <c r="N58" s="10"/>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" s="9"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -1874,11 +2172,13 @@
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="10"/>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="J59" s="25"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="10"/>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" s="9"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -1888,11 +2188,13 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="10"/>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="J60" s="25"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="10"/>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" s="9"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -1902,11 +2204,13 @@
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="10"/>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="J61" s="25"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="8"/>
+      <c r="M61" s="8"/>
+      <c r="N61" s="10"/>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" s="9"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -1916,11 +2220,13 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="10"/>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="J62" s="25"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="8"/>
+      <c r="M62" s="8"/>
+      <c r="N62" s="10"/>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" s="9"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -1930,11 +2236,13 @@
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="10"/>
-    </row>
-    <row r="64" spans="1:12">
+      <c r="J63" s="25"/>
+      <c r="K63" s="30"/>
+      <c r="L63" s="8"/>
+      <c r="M63" s="8"/>
+      <c r="N63" s="10"/>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64" s="9"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -1944,11 +2252,13 @@
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="10"/>
-    </row>
-    <row r="65" spans="1:12">
+      <c r="J64" s="25"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="8"/>
+      <c r="M64" s="8"/>
+      <c r="N64" s="10"/>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65" s="9"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -1958,11 +2268,13 @@
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="10"/>
-    </row>
-    <row r="66" spans="1:12">
+      <c r="J65" s="25"/>
+      <c r="K65" s="30"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="N65" s="10"/>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66" s="9"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -1972,11 +2284,13 @@
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="10"/>
-    </row>
-    <row r="67" spans="1:12">
+      <c r="J66" s="25"/>
+      <c r="K66" s="30"/>
+      <c r="L66" s="8"/>
+      <c r="M66" s="8"/>
+      <c r="N66" s="10"/>
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67" s="9"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -1986,11 +2300,13 @@
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="10"/>
-    </row>
-    <row r="68" spans="1:12">
+      <c r="J67" s="25"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="8"/>
+      <c r="M67" s="8"/>
+      <c r="N67" s="10"/>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68" s="9"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -2000,11 +2316,13 @@
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="10"/>
-    </row>
-    <row r="69" spans="1:12">
+      <c r="J68" s="25"/>
+      <c r="K68" s="30"/>
+      <c r="L68" s="8"/>
+      <c r="M68" s="8"/>
+      <c r="N68" s="10"/>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69" s="9"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -2014,11 +2332,13 @@
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="10"/>
-    </row>
-    <row r="70" spans="1:12">
+      <c r="J69" s="25"/>
+      <c r="K69" s="30"/>
+      <c r="L69" s="8"/>
+      <c r="M69" s="8"/>
+      <c r="N69" s="10"/>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70" s="9"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -2028,11 +2348,13 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="10"/>
-    </row>
-    <row r="71" spans="1:12">
+      <c r="J70" s="25"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+      <c r="N70" s="10"/>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71" s="9"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -2042,11 +2364,13 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="10"/>
-    </row>
-    <row r="72" spans="1:12">
+      <c r="J71" s="25"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="8"/>
+      <c r="N71" s="10"/>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72" s="9"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -2056,11 +2380,13 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="10"/>
-    </row>
-    <row r="73" spans="1:12">
+      <c r="J72" s="25"/>
+      <c r="K72" s="30"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="8"/>
+      <c r="N72" s="10"/>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73" s="9"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -2070,11 +2396,13 @@
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="10"/>
-    </row>
-    <row r="74" spans="1:12">
+      <c r="J73" s="25"/>
+      <c r="K73" s="30"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="8"/>
+      <c r="N73" s="10"/>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74" s="9"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -2084,11 +2412,13 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="10"/>
-    </row>
-    <row r="75" spans="1:12">
+      <c r="J74" s="25"/>
+      <c r="K74" s="30"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+      <c r="N74" s="10"/>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75" s="9"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -2098,11 +2428,13 @@
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
       <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="10"/>
-    </row>
-    <row r="76" spans="1:12" ht="14.25" thickBot="1">
+      <c r="J75" s="25"/>
+      <c r="K75" s="30"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="8"/>
+      <c r="N75" s="10"/>
+    </row>
+    <row r="76" spans="1:14" ht="14.25" thickBot="1">
       <c r="A76" s="11"/>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
@@ -2112,45 +2444,49 @@
       <c r="G76" s="12"/>
       <c r="H76" s="12"/>
       <c r="I76" s="12"/>
-      <c r="J76" s="12"/>
-      <c r="K76" s="12"/>
-      <c r="L76" s="13"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="31"/>
+      <c r="L76" s="12"/>
+      <c r="M76" s="12"/>
+      <c r="N76" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L44">
+  <autoFilter ref="A1:N44">
     <filterColumn colId="3"/>
     <filterColumn colId="5"/>
+    <filterColumn colId="8"/>
+    <filterColumn colId="9"/>
     <sortState ref="A2:M48">
       <sortCondition ref="A1:A48"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:L187">
-    <cfRule type="expression" dxfId="19" priority="29" stopIfTrue="1">
-      <formula>$J2="HANG-UP"</formula>
+  <conditionalFormatting sqref="A2:N187">
+    <cfRule type="expression" dxfId="23" priority="29" stopIfTrue="1">
+      <formula>$L2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="30" stopIfTrue="1">
-      <formula>$J2="PLAN"</formula>
+    <cfRule type="expression" dxfId="22" priority="30" stopIfTrue="1">
+      <formula>$L2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="31" stopIfTrue="1">
-      <formula>$J2="OPEN"</formula>
+    <cfRule type="expression" dxfId="21" priority="31" stopIfTrue="1">
+      <formula>$L2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="32" stopIfTrue="1">
-      <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
+    <cfRule type="expression" dxfId="20" priority="32" stopIfTrue="1">
+      <formula>OR($L2="CLOSED",$L2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="15" priority="1" stopIfTrue="1">
-      <formula>$J4="HANG-UP"</formula>
+    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
+      <formula>$L4="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2" stopIfTrue="1">
-      <formula>$J4="PLAN"</formula>
+    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+      <formula>$L4="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="3" stopIfTrue="1">
-      <formula>$J4="OPEN"</formula>
+    <cfRule type="expression" dxfId="17" priority="3" stopIfTrue="1">
+      <formula>$L4="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="4" stopIfTrue="1">
-      <formula>OR($J4="CLOSED",$J4="CANCEL")</formula>
+    <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
+      <formula>OR($L4="CLOSED",$L4="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -2160,7 +2496,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F76">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J76">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L76">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2174,34 +2510,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.5" customWidth="1"/>
+    <col min="1" max="1" width="5.625" customWidth="1"/>
     <col min="2" max="2" width="39.75" customWidth="1"/>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="9.375" customWidth="1"/>
-    <col min="6" max="6" width="9.75" customWidth="1"/>
-    <col min="7" max="7" width="9.875" customWidth="1"/>
-    <col min="8" max="8" width="14.125" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="15.875" customWidth="1"/>
-    <col min="12" max="12" width="17.375" customWidth="1"/>
+    <col min="3" max="3" width="24.75" customWidth="1"/>
+    <col min="4" max="4" width="8.75" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="9.375" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="9" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="10.375" customWidth="1"/>
+    <col min="12" max="12" width="9.375" customWidth="1"/>
+    <col min="13" max="13" width="12.5" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="29.45" customHeight="1">
+    <row r="1" spans="1:14" ht="29.45" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="5"/>
       <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
@@ -2214,286 +2553,330 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="5" t="s">
+      <c r="N1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="9"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="10"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="9"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
       <c r="I3" s="8"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="10"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="9"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="10"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="9"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="10"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="9"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="20"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="1"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="10"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="10"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="9"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="1"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="10"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="9"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="10"/>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="1"/>
       <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="C10" s="21"/>
       <c r="D10" s="8"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="1"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="9"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="1"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="10"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="9"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="1"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="10"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="9"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="1"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="10"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="9"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="10"/>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="9"/>
       <c r="B15" s="8"/>
-      <c r="C15" s="23"/>
+      <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="J15" s="25"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="10"/>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="9"/>
       <c r="B16" s="8"/>
-      <c r="C16" s="23"/>
+      <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="10"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="1"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="9"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="23"/>
+      <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="22"/>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="1"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="10"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="9"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="15"/>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="1"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="10"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="9"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="10"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="9"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2503,11 +2886,13 @@
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="10"/>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="J21" s="25"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="10"/>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="9"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -2517,11 +2902,13 @@
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="10"/>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="J22" s="25"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="10"/>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="9"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -2531,11 +2918,13 @@
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="J23" s="25"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="10"/>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="9"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -2545,11 +2934,13 @@
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="10"/>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="J24" s="25"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="10"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="9"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -2559,11 +2950,13 @@
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="10"/>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="J25" s="25"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="10"/>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="9"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -2573,11 +2966,13 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="10"/>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="J26" s="25"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="10"/>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="9"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -2587,11 +2982,13 @@
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="10"/>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="J27" s="25"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="10"/>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="9"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -2601,11 +2998,13 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="10"/>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="J28" s="25"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="10"/>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="9"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -2615,11 +3014,13 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="10"/>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="J29" s="25"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="10"/>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="9"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -2629,11 +3030,13 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="10"/>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="J30" s="25"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="10"/>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="9"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -2643,11 +3046,13 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="10"/>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="J31" s="25"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="10"/>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="9"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -2657,11 +3062,13 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="10"/>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="J32" s="25"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="10"/>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="9"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -2671,80 +3078,310 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="10"/>
-    </row>
-    <row r="34" spans="1:12" ht="14.25" thickBot="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="13"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="10"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="9"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="10"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="9"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="10"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="9"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="10"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="9"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="10"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="9"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="10"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="9"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="10"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="9"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="10"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="9"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="10"/>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="9"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="10"/>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="9"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="10"/>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="9"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="10"/>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="9"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="25"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="10"/>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="9"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="10"/>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="9"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="25"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="10"/>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="9"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="10"/>
+    </row>
+    <row r="49" spans="1:14" ht="14.25" thickBot="1">
+      <c r="A49" s="11"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="26"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
+      <c r="N49" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L24">
+  <autoFilter ref="A1:L2">
     <filterColumn colId="2"/>
     <filterColumn colId="3"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:L18">
-    <cfRule type="expression" dxfId="11" priority="137" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:L2">
+    <cfRule type="expression" dxfId="7" priority="145" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="138" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="146" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="139" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="147" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="140" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="148" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="7" priority="129" stopIfTrue="1">
-      <formula>$J5="HANG-UP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="130" stopIfTrue="1">
-      <formula>$J5="PLAN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="131" stopIfTrue="1">
-      <formula>$J5="OPEN"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="132" stopIfTrue="1">
-      <formula>OR($J5="CLOSED",$J5="CANCEL")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17">
+  <conditionalFormatting sqref="A2:N160">
     <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
-      <formula>$J17="HANG-UP"</formula>
+      <formula>$L2="HANG-UP"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="6" stopIfTrue="1">
-      <formula>$J17="PLAN"</formula>
+      <formula>$L2="PLAN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
-      <formula>$J17="OPEN"</formula>
+      <formula>$L2="OPEN"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
-      <formula>OR($J17="CLOSED",$J17="CANCEL")</formula>
+      <formula>OR($L2="CLOSED",$L2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J34">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L49">
       <formula1>"PLAN,OPEN,CANCEL,CLOSED,HANG-UP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F34">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F49">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E34">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E49">
       <formula1>"Bug,可靠性,性能,可维护性,易用性,可测试性,功能,优化"</formula1>
     </dataValidation>
   </dataValidations>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
   <si>
     <r>
       <t>描述</t>
@@ -231,6 +231,14 @@
     <t>发现时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一些常见服务的配置整理成文档，及配置过程中遇到过的问题（包括平台、问题、及解决办法）也整理在其中，如(hadoop,mongodb,SSH无密码访问,ntpd配置本地时间同步服务器等)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -652,91 +660,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill>
@@ -1314,16 +1238,22 @@
         <v>42151</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="1"/>
-      <c r="B6" s="8"/>
+    <row r="6" spans="1:14" ht="54">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="J6" s="23"/>
       <c r="K6" s="28"/>
       <c r="L6" s="2"/>
@@ -2462,30 +2392,30 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:N187">
-    <cfRule type="expression" dxfId="23" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="29" stopIfTrue="1">
       <formula>$L2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="30" stopIfTrue="1">
       <formula>$L2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="31" stopIfTrue="1">
       <formula>$L2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="32" stopIfTrue="1">
       <formula>OR($L2="CLOSED",$L2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
       <formula>$L4="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
       <formula>$L4="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
       <formula>$L4="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
       <formula>OR($L4="CLOSED",$L4="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
   <si>
     <r>
       <t>描述</t>
@@ -239,6 +239,27 @@
     <t>一些常见服务的配置整理成文档，及配置过程中遇到过的问题（包括平台、问题、及解决办法）也整理在其中，如(hadoop,mongodb,SSH无密码访问,ntpd配置本地时间同步服务器等)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>dropUsr参数输入错误时，报错不准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-902</t>
+  </si>
+  <si>
+    <t>Bug</t>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>SPT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -555,7 +576,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -655,12 +676,155 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="36">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1261,20 +1425,44 @@
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="1"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>31</v>
+      </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="3"/>
+      <c r="I7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="32">
+        <v>42160</v>
+      </c>
+      <c r="K7" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="32">
+        <v>42160</v>
+      </c>
+      <c r="N7" s="32">
+        <v>42160</v>
+      </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1"/>
@@ -2391,32 +2579,46 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:N187">
-    <cfRule type="expression" dxfId="15" priority="29" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:A187 B2:C6 B8:C187 D2:N187">
+    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
       <formula>$L2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
       <formula>$L2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
       <formula>$L2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
       <formula>OR($L2="CLOSED",$L2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="5" stopIfTrue="1">
       <formula>$L4="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="6" stopIfTrue="1">
       <formula>$L4="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="7" stopIfTrue="1">
       <formula>$L4="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="8" stopIfTrue="1">
       <formula>OR($L4="CLOSED",$L4="CANCEL")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
+      <formula>$L7="HANG-UP"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+      <formula>$L7="PLAN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3" stopIfTrue="1">
+      <formula>$L7="OPEN"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
+      <formula>OR($L7="CLOSED",$L7="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -2432,9 +2634,10 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1"/>
+    <hyperlink ref="C7" r:id="rId2" display="http://jira:8080/browse/SEQUOIADBMAINSTREAM-902"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -3277,30 +3480,30 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L2">
-    <cfRule type="expression" dxfId="7" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="145" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="146" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="147" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="148" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:N160">
-    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="5" stopIfTrue="1">
       <formula>$L2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="6" stopIfTrue="1">
       <formula>$L2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="7" stopIfTrue="1">
       <formula>$L2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="8" stopIfTrue="1">
       <formula>OR($L2="CLOSED",$L2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <r>
       <t>描述</t>
@@ -258,6 +258,22 @@
   </si>
   <si>
     <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mthMatch中对匹配条件解释生成LME中toMatch字段对 $gt, $lt和 $in,$all等的处理不一致；$gt会把$ge名字去掉，但$in不会去除；最好能做到统一（且性能最佳）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>许建辉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -684,119 +700,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill>
@@ -1464,17 +1368,31 @@
         <v>42160</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="1"/>
-      <c r="B8" s="8"/>
+    <row r="8" spans="1:14" ht="67.5">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="23"/>
+      <c r="I8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="32">
+        <v>42194</v>
+      </c>
       <c r="K8" s="28"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -2580,44 +2498,44 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:A187 B2:C6 B8:C187 D2:N187">
-    <cfRule type="expression" dxfId="35" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="33" stopIfTrue="1">
       <formula>$L2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="34" stopIfTrue="1">
       <formula>$L2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="35" stopIfTrue="1">
       <formula>$L2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="36" stopIfTrue="1">
       <formula>OR($L2="CLOSED",$L2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="31" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
       <formula>$L4="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="6" stopIfTrue="1">
       <formula>$L4="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
       <formula>$L4="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
       <formula>OR($L4="CLOSED",$L4="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
       <formula>$L7="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
       <formula>$L7="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
       <formula>$L7="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
       <formula>OR($L7="CLOSED",$L7="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3480,30 +3398,30 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:L2">
-    <cfRule type="expression" dxfId="27" priority="145" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="145" stopIfTrue="1">
       <formula>$J2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="146" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="146" stopIfTrue="1">
       <formula>$J2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="147" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="147" stopIfTrue="1">
       <formula>$J2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="148" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="148" stopIfTrue="1">
       <formula>OR($J2="CLOSED",$J2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:N160">
-    <cfRule type="expression" dxfId="23" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
       <formula>$L2="HANG-UP"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="6" stopIfTrue="1">
       <formula>$L2="PLAN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
       <formula>$L2="OPEN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
       <formula>OR($L2="CLOSED",$L2="CANCEL")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
+++ b/internal_doc/00.项目管理/00.任务计划/SequoiaDB持续改进跟踪表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
   <si>
     <r>
       <t>描述</t>
@@ -275,6 +275,24 @@
   <si>
     <t>许建辉</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbCloseAllCursors接口是否要开放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能</t>
+  </si>
+  <si>
+    <t>CLIENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭钊波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLAN</t>
   </si>
 </sst>
 </file>
@@ -1399,18 +1417,34 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="1"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="23"/>
+      <c r="I9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="32">
+        <v>42195</v>
+      </c>
       <c r="K9" s="28"/>
-      <c r="L9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="3"/>
     </row>
